--- a/data/trans_orig/Q5408-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5408-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar el bater en 2007</t>
+          <t>Población según si es capaz de usar el bater en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,97 +733,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2343</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1837</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7868</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>5,26%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2343</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8061</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>8240</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2343</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>7017</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13786</t>
+          <t>13305</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3386</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15258</t>
+          <t>15590</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8512</t>
+          <t>8763</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23393</t>
+          <t>24129</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>101203</t>
+          <t>101684</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>112109</t>
+          <t>111443</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>131495</t>
+          <t>132142</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>144854</t>
+          <t>145004</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>237917</t>
+          <t>236789</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>254270</t>
+          <t>254124</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -1189,97 +1189,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1903</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>6625</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>1320</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>7685</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>6602</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1320</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>7502</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10653</t>
+          <t>10397</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>3876</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16886</t>
+          <t>17637</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6653</t>
+          <t>6833</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>21554</t>
+          <t>22193</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>135236</t>
+          <t>135492</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>144068</t>
+          <t>144075</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>164548</t>
+          <t>163702</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>178174</t>
+          <t>177803</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>305596</t>
+          <t>304511</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>321146</t>
+          <t>320527</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -1645,97 +1645,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1942</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1848</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>1897</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>885</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7250</t>
+          <t>8415</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18200</t>
+          <t>18142</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>7086</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21376</t>
+          <t>22209</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>97121</t>
+          <t>95956</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>103487</t>
+          <t>103486</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>117650</t>
+          <t>117708</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>130967</t>
+          <t>130702</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>218845</t>
+          <t>218012</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>233370</t>
+          <t>233135</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6843</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>910</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9243</t>
+          <t>9239</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>801</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7077</t>
+          <t>6802</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11181</t>
+          <t>12291</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3671</t>
+          <t>3466</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15219</t>
+          <t>15387</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>127848</t>
+          <t>127487</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>135584</t>
+          <t>135574</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>194834</t>
+          <t>194442</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>205438</t>
+          <t>205604</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>325509</t>
+          <t>326156</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>339379</t>
+          <t>339962</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2082</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12166</t>
+          <t>12641</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14334</t>
+          <t>14999</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11016</t>
+          <t>10443</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25619</t>
+          <t>25780</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21517</t>
+          <t>21485</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>45873</t>
+          <t>46508</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>36771</t>
+          <t>36346</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>64134</t>
+          <t>63735</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>474333</t>
+          <t>474144</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>490015</t>
+          <t>490459</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>625105</t>
+          <t>624222</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>651198</t>
+          <t>650411</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1107353</t>
+          <t>1107294</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1136569</t>
+          <t>1136691</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,39%</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar el bater en 2012</t>
+          <t>Población según si es capaz de usar el bater en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7318</t>
+          <t>7310</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7084</t>
+          <t>6395</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9669</t>
+          <t>9537</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9347</t>
+          <t>9350</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>4349</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18466</t>
+          <t>17357</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7390</t>
+          <t>7518</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22350</t>
+          <t>21440</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>127077</t>
+          <t>127796</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>137482</t>
+          <t>137456</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>146274</t>
+          <t>147053</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>160319</t>
+          <t>160677</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>278414</t>
+          <t>279217</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>295786</t>
+          <t>295682</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,52%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9570</t>
+          <t>10060</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2311</t>
+          <t>3053</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13327</t>
+          <t>12919</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18843</t>
+          <t>17729</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4450</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17799</t>
+          <t>17813</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9214</t>
+          <t>10139</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25927</t>
+          <t>26337</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>17063</t>
+          <t>17745</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>37480</t>
+          <t>39150</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>133063</t>
+          <t>131570</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>147387</t>
+          <t>147304</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>157252</t>
+          <t>158680</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>176474</t>
+          <t>176416</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>294668</t>
+          <t>296254</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>319935</t>
+          <t>319386</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,23%</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13016</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>2197</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14903</t>
+          <t>15118</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4365</t>
+          <t>4323</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20468</t>
+          <t>20257</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11333</t>
+          <t>10771</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5069</t>
+          <t>5113</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17019</t>
+          <t>16624</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8400</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24170</t>
+          <t>24349</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>86271</t>
+          <t>86989</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>99527</t>
+          <t>100419</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>114545</t>
+          <t>115695</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>131255</t>
+          <t>131963</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>208380</t>
+          <t>207168</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>229274</t>
+          <t>228605</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4901</t>
+          <t>5637</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9592</t>
+          <t>10460</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11175</t>
+          <t>11553</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15896</t>
+          <t>14567</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5374</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17698</t>
+          <t>18870</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10133</t>
+          <t>10274</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27939</t>
+          <t>27159</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>144853</t>
+          <t>144986</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>157814</t>
+          <t>158563</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>219287</t>
+          <t>219932</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>234744</t>
+          <t>235402</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>372397</t>
+          <t>372719</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>391425</t>
+          <t>390699</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5088</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20054</t>
+          <t>19167</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11833</t>
+          <t>11795</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30655</t>
+          <t>30792</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19902</t>
+          <t>21054</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>43542</t>
+          <t>44466</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17673</t>
+          <t>16981</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>38257</t>
+          <t>38182</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>33252</t>
+          <t>33465</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>61334</t>
+          <t>63580</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>56652</t>
+          <t>56470</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>90805</t>
+          <t>91430</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>509032</t>
+          <t>509512</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>533280</t>
+          <t>533224</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>660775</t>
+          <t>657950</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>692149</t>
+          <t>691615</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1179472</t>
+          <t>1176887</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1219146</t>
+          <t>1218235</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,52%</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar el bater en 2016</t>
+          <t>Población según si es capaz de usar el bater en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>881</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8876</t>
+          <t>8432</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8224</t>
+          <t>7328</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2417</t>
+          <t>2461</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12347</t>
+          <t>12450</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3436</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14463</t>
+          <t>13798</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2894</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14579</t>
+          <t>13877</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>8554</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23233</t>
+          <t>22952</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>117749</t>
+          <t>117679</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>130563</t>
+          <t>130137</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>155397</t>
+          <t>155896</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>168849</t>
+          <t>168956</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>280060</t>
+          <t>279976</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>297969</t>
+          <t>297129</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4135</t>
+          <t>4122</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11770</t>
+          <t>13311</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13394</t>
+          <t>13620</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4224</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14800</t>
+          <t>14666</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>5178</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21150</t>
+          <t>20553</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>12224</t>
+          <t>11520</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>30205</t>
+          <t>30501</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>149333</t>
+          <t>149007</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>160692</t>
+          <t>159850</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>192439</t>
+          <t>193717</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>210461</t>
+          <t>210596</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>348068</t>
+          <t>345052</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>368126</t>
+          <t>367662</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -6669,97 +6669,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1918</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>8459</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>5,93%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>2618</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>8937</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>7944</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>6,27%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>9309</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>805</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7426</t>
+          <t>7423</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6155</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20056</t>
+          <t>19854</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8317</t>
+          <t>7714</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24401</t>
+          <t>24516</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>107609</t>
+          <t>107612</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>114233</t>
+          <t>114230</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,7 +6910,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>119748</t>
+          <t>119422</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>135042</t>
+          <t>135027</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>230513</t>
+          <t>230497</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>247918</t>
+          <t>248095</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7256</t>
+          <t>6884</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10056</t>
+          <t>9822</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12530</t>
+          <t>11481</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9658</t>
+          <t>10142</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13140</t>
+          <t>12364</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4708</t>
+          <t>4199</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19410</t>
+          <t>17648</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>162366</t>
+          <t>162494</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>172242</t>
+          <t>172466</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>225912</t>
+          <t>225493</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>239031</t>
+          <t>238982</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>392371</t>
+          <t>392078</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>408979</t>
+          <t>409042</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2419</t>
+          <t>2427</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11749</t>
+          <t>11545</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6316</t>
+          <t>6336</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23024</t>
+          <t>24655</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10631</t>
+          <t>10866</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30839</t>
+          <t>30102</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16112</t>
+          <t>15626</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34329</t>
+          <t>34446</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>23666</t>
+          <t>24271</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50279</t>
+          <t>50007</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>43991</t>
+          <t>45069</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>74751</t>
+          <t>75287</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>550747</t>
+          <t>550407</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>571065</t>
+          <t>570953</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>712568</t>
+          <t>711792</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>742506</t>
+          <t>743047</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1271509</t>
+          <t>1271483</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1307962</t>
+          <t>1308108</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7897,7 +7897,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -8074,7 +8074,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar el bater en 2023</t>
+          <t>Población según si es capaz de usar el bater en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>362</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6573</t>
+          <t>6800</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8078</t>
+          <t>8647</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9233</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10907</t>
+          <t>10475</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20025</t>
+          <t>19524</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15478</t>
+          <t>15694</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26287</t>
+          <t>26291</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,7 +8467,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>137116</t>
+          <t>135609</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>144169</t>
+          <t>143659</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>155232</t>
+          <t>155547</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>165443</t>
+          <t>165411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>295557</t>
+          <t>295322</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>307332</t>
+          <t>307462</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,95%</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7442</t>
+          <t>7247</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2765</t>
+          <t>2589</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8881</t>
+          <t>8381</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11504</t>
+          <t>11611</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13293</t>
+          <t>13435</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25916</t>
+          <t>25644</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>19011</t>
+          <t>18702</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>34434</t>
+          <t>33639</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>147105</t>
+          <t>147252</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155739</t>
+          <t>155606</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>187543</t>
+          <t>188094</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>201425</t>
+          <t>201424</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>338820</t>
+          <t>339643</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>354699</t>
+          <t>354947</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,83%</t>
         </is>
       </c>
     </row>
@@ -9186,7 +9186,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11502</t>
+          <t>10537</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>723</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11332</t>
+          <t>11530</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>673</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>6984</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27603</t>
+          <t>24617</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2914</t>
+          <t>2699</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24943</t>
+          <t>23581</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>127597</t>
+          <t>126675</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>135564</t>
+          <t>135466</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>323759</t>
+          <t>327468</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>357386</t>
+          <t>357576</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>464638</t>
+          <t>464329</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>492653</t>
+          <t>492324</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>5124</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2902</t>
+          <t>2608</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9598</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11829</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1702</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t>8528</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t>8540</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19800</t>
+          <t>19455</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11491</t>
+          <t>11569</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24619</t>
+          <t>24097</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>194482</t>
+          <t>194557</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>202324</t>
+          <t>201926</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>250116</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>262891</t>
+          <t>262981</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>448856</t>
+          <t>448774</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>463690</t>
+          <t>462894</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,31%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>2473</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10829</t>
+          <t>10568</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7843</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24081</t>
+          <t>23940</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13018</t>
+          <t>13574</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30238</t>
+          <t>30493</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12975</t>
+          <t>13451</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>27211</t>
+          <t>28006</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30216</t>
+          <t>29721</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>75617</t>
+          <t>76099</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>49793</t>
+          <t>49871</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>92523</t>
+          <t>93261</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>616716</t>
+          <t>616380</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>632545</t>
+          <t>631884</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>936975</t>
+          <t>936266</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>994233</t>
+          <t>995017</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1565372</t>
+          <t>1565004</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1619308</t>
+          <t>1618603</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5408-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5408-Habitat-trans_orig.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7868</t>
+          <t>7807</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>7253</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3546</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13305</t>
+          <t>13046</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15590</t>
+          <t>15317</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8763</t>
+          <t>8475</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24129</t>
+          <t>23776</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>101684</t>
+          <t>101943</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>111443</t>
+          <t>111440</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>132142</t>
+          <t>130925</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>145004</t>
+          <t>144241</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>236789</t>
+          <t>236827</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>254124</t>
+          <t>253970</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,01%</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>6674</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6602</t>
+          <t>7808</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10397</t>
+          <t>9535</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3876</t>
+          <t>3606</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17637</t>
+          <t>16699</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6833</t>
+          <t>7059</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>22193</t>
+          <t>22128</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>135492</t>
+          <t>136354</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>144075</t>
+          <t>144860</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>163702</t>
+          <t>163433</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>177803</t>
+          <t>178133</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>304511</t>
+          <t>304141</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>320527</t>
+          <t>320497</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>872</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8415</t>
+          <t>7696</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18142</t>
+          <t>18169</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7086</t>
+          <t>6886</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22209</t>
+          <t>21581</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>95956</t>
+          <t>96675</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>103486</t>
+          <t>103499</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>117708</t>
+          <t>117681</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>130702</t>
+          <t>131067</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>218012</t>
+          <t>218640</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>233135</t>
+          <t>233335</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5086</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6843</t>
+          <t>6524</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>898</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9239</t>
+          <t>8608</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>6810</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2079</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12291</t>
+          <t>12481</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3466</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15387</t>
+          <t>14935</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>127487</t>
+          <t>127891</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>135574</t>
+          <t>135573</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>194442</t>
+          <t>193722</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>205604</t>
+          <t>205615</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>326156</t>
+          <t>326513</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>339962</t>
+          <t>339889</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>6204</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12641</t>
+          <t>12102</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14999</t>
+          <t>16262</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10443</t>
+          <t>11197</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25780</t>
+          <t>26246</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21485</t>
+          <t>22058</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>46508</t>
+          <t>44987</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>36346</t>
+          <t>34743</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>63735</t>
+          <t>63138</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>474144</t>
+          <t>474315</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>490459</t>
+          <t>489966</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>624222</t>
+          <t>625202</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>650411</t>
+          <t>649307</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1107294</t>
+          <t>1108311</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1136691</t>
+          <t>1137175</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>6449</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6395</t>
+          <t>7420</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9537</t>
+          <t>11317</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>964</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9350</t>
+          <t>9261</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4349</t>
+          <t>4315</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17357</t>
+          <t>16434</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7518</t>
+          <t>7493</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21440</t>
+          <t>22217</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>127796</t>
+          <t>126594</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>137456</t>
+          <t>137488</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>147053</t>
+          <t>147345</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>160677</t>
+          <t>160627</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>279217</t>
+          <t>278061</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>295682</t>
+          <t>295638</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>998</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10060</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>2232</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12919</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>5189</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17729</t>
+          <t>18485</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4651</t>
+          <t>4490</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17813</t>
+          <t>17602</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10139</t>
+          <t>9737</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26337</t>
+          <t>26707</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>17745</t>
+          <t>17171</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>39150</t>
+          <t>38519</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>131570</t>
+          <t>132073</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>147304</t>
+          <t>147166</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>158680</t>
+          <t>157339</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>176416</t>
+          <t>176704</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>296254</t>
+          <t>296349</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>319386</t>
+          <t>319635</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,3%</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>12773</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2197</t>
+          <t>2256</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15118</t>
+          <t>14438</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>4342</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20257</t>
+          <t>18754</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10771</t>
+          <t>10865</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5113</t>
+          <t>4497</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16624</t>
+          <t>17558</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8149</t>
+          <t>8630</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24349</t>
+          <t>23767</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>86989</t>
+          <t>87160</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>100419</t>
+          <t>100328</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>115695</t>
+          <t>115815</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>131963</t>
+          <t>131808</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>207168</t>
+          <t>207684</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>228605</t>
+          <t>227963</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,19%</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5637</t>
+          <t>4964</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10460</t>
+          <t>10291</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11553</t>
+          <t>11237</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2848</t>
+          <t>2983</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14567</t>
+          <t>15734</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5374</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18870</t>
+          <t>19496</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10274</t>
+          <t>9528</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27159</t>
+          <t>27416</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>144986</t>
+          <t>145181</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>158563</t>
+          <t>157716</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>219932</t>
+          <t>219935</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>235402</t>
+          <t>235286</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>372719</t>
+          <t>371490</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>390699</t>
+          <t>391059</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19167</t>
+          <t>19239</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11795</t>
+          <t>11881</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30792</t>
+          <t>30071</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>21054</t>
+          <t>19779</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>44466</t>
+          <t>43129</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16981</t>
+          <t>17218</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>38182</t>
+          <t>38520</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>33465</t>
+          <t>33164</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>63580</t>
+          <t>60314</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>56470</t>
+          <t>55928</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>91430</t>
+          <t>91242</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>509512</t>
+          <t>509255</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>533224</t>
+          <t>532930</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>657950</t>
+          <t>661567</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>691615</t>
+          <t>694105</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1176887</t>
+          <t>1179295</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1218235</t>
+          <t>1218334</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>853</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8432</t>
+          <t>8469</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>8418</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2461</t>
+          <t>2427</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12450</t>
+          <t>12838</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3899</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13798</t>
+          <t>13023</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2894</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13877</t>
+          <t>13452</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8554</t>
+          <t>7866</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22952</t>
+          <t>23230</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>117679</t>
+          <t>119584</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>130137</t>
+          <t>130569</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>155896</t>
+          <t>157158</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>168956</t>
+          <t>169998</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>279976</t>
+          <t>280518</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>297129</t>
+          <t>298271</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>96,18%</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4122</t>
+          <t>4994</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13311</t>
+          <t>13737</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>13444</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>4319</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14666</t>
+          <t>15638</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5178</t>
+          <t>5390</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20553</t>
+          <t>21005</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11520</t>
+          <t>12124</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>30501</t>
+          <t>29682</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>149007</t>
+          <t>148502</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>159850</t>
+          <t>159861</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>193717</t>
+          <t>191935</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>210596</t>
+          <t>209882</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>345052</t>
+          <t>346709</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>367662</t>
+          <t>367415</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -6709,7 +6709,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8459</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7944</t>
+          <t>9185</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>812</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7423</t>
+          <t>7374</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>5228</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19854</t>
+          <t>19325</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7714</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24516</t>
+          <t>23200</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>107612</t>
+          <t>107661</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>114230</t>
+          <t>114223</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>119422</t>
+          <t>119308</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>135027</t>
+          <t>135089</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>230497</t>
+          <t>229806</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>248095</t>
+          <t>247746</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6884</t>
+          <t>6487</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9822</t>
+          <t>10187</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11481</t>
+          <t>12450</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10142</t>
+          <t>10588</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12364</t>
+          <t>12853</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4199</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17648</t>
+          <t>18919</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>162494</t>
+          <t>162136</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>172466</t>
+          <t>172413</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>225493</t>
+          <t>224977</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>238982</t>
+          <t>238896</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>392078</t>
+          <t>392610</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>409042</t>
+          <t>408863</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2427</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11545</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6336</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24655</t>
+          <t>23731</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10866</t>
+          <t>11442</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30102</t>
+          <t>30054</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15626</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34446</t>
+          <t>34177</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24271</t>
+          <t>25011</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50007</t>
+          <t>50311</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>45069</t>
+          <t>44853</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>75287</t>
+          <t>74996</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>550407</t>
+          <t>551194</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>570953</t>
+          <t>571412</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>711792</t>
+          <t>713049</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>743047</t>
+          <t>742614</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1271483</t>
+          <t>1272896</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1308108</t>
+          <t>1308889</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>
@@ -8264,32 +8264,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>477</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>3570</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8299,32 +8299,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1501</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6800</t>
+          <t>6663</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8334,32 +8334,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8647</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -8377,32 +8377,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3048</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>9534</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8412,32 +8412,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14823</t>
+          <t>15199</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10475</t>
+          <t>10850</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19524</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8447,32 +8447,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>20351</t>
+          <t>20800</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15694</t>
+          <t>15176</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26291</t>
+          <t>27621</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -8490,32 +8490,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>141035</t>
+          <t>156197</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>135609</t>
+          <t>151912</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>143659</t>
+          <t>158966</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8525,32 +8525,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>160949</t>
+          <t>172363</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>155547</t>
+          <t>166532</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>165411</t>
+          <t>177212</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8560,32 +8560,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>301985</t>
+          <t>328560</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>295322</t>
+          <t>321435</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>307462</t>
+          <t>334843</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,5%</t>
         </is>
       </c>
     </row>
@@ -8603,17 +8603,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8673,17 +8673,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>1126</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3646</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8755,32 +8755,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3824</t>
+          <t>4242</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7247</t>
+          <t>8433</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8790,32 +8790,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4927</t>
+          <t>5368</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2589</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8381</t>
+          <t>9352</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -8833,32 +8833,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6979</t>
+          <t>7145</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3605</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11611</t>
+          <t>12088</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8868,32 +8868,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18790</t>
+          <t>19640</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13435</t>
+          <t>13727</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25644</t>
+          <t>26872</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8903,32 +8903,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>25769</t>
+          <t>26785</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>18702</t>
+          <t>20294</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>33639</t>
+          <t>35763</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -8946,32 +8946,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>152032</t>
+          <t>169932</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>147252</t>
+          <t>164820</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155606</t>
+          <t>173631</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8981,32 +8981,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>195553</t>
+          <t>217470</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>188094</t>
+          <t>209490</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>201424</t>
+          <t>223602</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9016,32 +9016,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>347585</t>
+          <t>387402</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>339643</t>
+          <t>377196</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>354947</t>
+          <t>394535</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>94,04%</t>
         </is>
       </c>
     </row>
@@ -9059,17 +9059,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9094,17 +9094,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>218167</t>
+          <t>241351</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>218167</t>
+          <t>241351</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>218167</t>
+          <t>241351</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9129,17 +9129,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>378282</t>
+          <t>419555</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>378282</t>
+          <t>419555</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>378282</t>
+          <t>419555</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9211,32 +9211,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3574</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10537</t>
+          <t>9295</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9246,32 +9246,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11530</t>
+          <t>10989</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -9289,32 +9289,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>875</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6984</t>
+          <t>7897</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9324,32 +9324,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9744</t>
+          <t>10477</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>6430</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24617</t>
+          <t>16157</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9359,32 +9359,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>12710</t>
+          <t>13866</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2699</t>
+          <t>8550</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23581</t>
+          <t>20346</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -9402,32 +9402,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>132785</t>
+          <t>155062</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>126675</t>
+          <t>149932</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>135466</t>
+          <t>158208</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9437,32 +9437,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>346938</t>
+          <t>160497</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>327468</t>
+          <t>153694</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>357576</t>
+          <t>165807</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9472,32 +9472,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>479723</t>
+          <t>315558</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>464329</t>
+          <t>307643</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>492324</t>
+          <t>322155</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -9515,17 +9515,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9550,17 +9550,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9585,17 +9585,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9632,32 +9632,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>612</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5124</t>
+          <t>5509</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9667,32 +9667,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5341</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>10425</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9702,32 +9702,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>7979</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11696</t>
+          <t>13075</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -9745,32 +9745,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4108</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>1889</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9780,32 +9780,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13021</t>
+          <t>14537</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8540</t>
+          <t>9289</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19455</t>
+          <t>22682</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9815,32 +9815,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>17128</t>
+          <t>18716</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11569</t>
+          <t>12576</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24097</t>
+          <t>27420</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -9858,32 +9858,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>199418</t>
+          <t>208994</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>194557</t>
+          <t>204461</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>201926</t>
+          <t>212028</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9893,32 +9893,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>257262</t>
+          <t>274766</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>250354</t>
+          <t>266430</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>262981</t>
+          <t>281007</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9928,32 +9928,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>456680</t>
+          <t>483759</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>448774</t>
+          <t>474802</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>462894</t>
+          <t>491167</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -9971,17 +9971,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10006,17 +10006,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>480653</t>
+          <t>510454</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>480653</t>
+          <t>510454</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>480653</t>
+          <t>510454</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10088,17 +10088,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5329</t>
+          <t>5892</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2473</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10568</t>
+          <t>11669</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10123,32 +10123,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>16130</t>
+          <t>17707</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8128</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23940</t>
+          <t>26107</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10158,32 +10158,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>21459</t>
+          <t>23599</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13574</t>
+          <t>17302</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30493</t>
+          <t>32008</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -10201,32 +10201,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>19580</t>
+          <t>20315</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13451</t>
+          <t>14202</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>28006</t>
+          <t>28647</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10236,32 +10236,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>56378</t>
+          <t>59852</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29721</t>
+          <t>47981</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>76099</t>
+          <t>71184</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10271,32 +10271,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>75958</t>
+          <t>80167</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>49871</t>
+          <t>68259</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>93261</t>
+          <t>94457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -10314,32 +10314,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>625269</t>
+          <t>690184</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>616380</t>
+          <t>681014</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>631884</t>
+          <t>697588</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10349,32 +10349,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>960703</t>
+          <t>825096</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>936266</t>
+          <t>813081</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>995017</t>
+          <t>838237</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10384,32 +10384,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1585972</t>
+          <t>1515280</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1565004</t>
+          <t>1499223</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1618603</t>
+          <t>1528316</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>94,4%</t>
         </is>
       </c>
     </row>
@@ -10427,17 +10427,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10462,17 +10462,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1033211</t>
+          <t>902655</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1033211</t>
+          <t>902655</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1033211</t>
+          <t>902655</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10497,17 +10497,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1683389</t>
+          <t>1619046</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1683389</t>
+          <t>1619046</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1683389</t>
+          <t>1619046</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
